--- a/salidas/empresas/NVDA.xlsx
+++ b/salidas/empresas/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3427057266235352</v>
+        <v>0.3427056968212128</v>
       </c>
       <c r="C2" t="n">
         <v>0.3746669888496399</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3592460453510284</v>
+        <v>0.3592460751533508</v>
       </c>
       <c r="C3" t="n">
         <v>0.3927499949932098</v>
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3503278195858002</v>
+        <v>0.3503278493881226</v>
       </c>
       <c r="C6" t="n">
         <v>0.382999986410141</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3245637118816376</v>
+        <v>0.3245636522769928</v>
       </c>
       <c r="C7" t="n">
         <v>0.3548330068588257</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3375221490859985</v>
+        <v>0.3375221788883209</v>
       </c>
       <c r="C8" t="n">
         <v>0.3689999878406525</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437792599201202</v>
+        <v>0.4437792897224426</v>
       </c>
       <c r="C9" t="n">
         <v>0.485166996717453</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4510969519615173</v>
+        <v>0.4510968327522278</v>
       </c>
       <c r="C10" t="n">
         <v>0.4931670129299164</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5315901637077332</v>
+        <v>0.5315897464752197</v>
       </c>
       <c r="C11" t="n">
         <v>0.5811669826507568</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5639088153839111</v>
+        <v>0.5639087557792664</v>
       </c>
       <c r="C12" t="n">
         <v>0.6165000200271606</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4672559499740601</v>
+        <v>0.4672559201717377</v>
       </c>
       <c r="C14" t="n">
         <v>0.5108330249786377</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>0.472592294216156</v>
+        <v>0.4725921750068665</v>
       </c>
       <c r="C15" t="n">
         <v>0.5166670083999634</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4387485086917877</v>
+        <v>0.4387485384941101</v>
       </c>
       <c r="C16" t="n">
         <v>0.4796670079231262</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5014049410820007</v>
+        <v>0.5014051198959351</v>
       </c>
       <c r="C17" t="n">
         <v>0.5481669902801514</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5280831456184387</v>
+        <v>0.5280829668045044</v>
       </c>
       <c r="C18" t="n">
         <v>0.5773329734802246</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6297668218612671</v>
+        <v>0.6297668814659119</v>
       </c>
       <c r="C19" t="n">
         <v>0.6884999871253967</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6976070404052734</v>
+        <v>0.6976071000099182</v>
       </c>
       <c r="C20" t="n">
         <v>0.7626670002937317</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7799293398857117</v>
+        <v>0.7799292802810669</v>
       </c>
       <c r="C21" t="n">
         <v>0.852666974067688</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>0.8287128210067749</v>
+        <v>0.8287127614021301</v>
       </c>
       <c r="C22" t="n">
         <v>0.906000018119812</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>0.7212362289428711</v>
+        <v>0.7212361693382263</v>
       </c>
       <c r="C24" t="n">
         <v>0.7885000109672546</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>0.7779472470283508</v>
+        <v>0.7779473662376404</v>
       </c>
       <c r="C25" t="n">
         <v>0.8504999876022339</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>0.4891328513622284</v>
+        <v>0.4891325533390045</v>
       </c>
       <c r="C27" t="n">
         <v>0.5347499847412109</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>0.4525448679924011</v>
+        <v>0.4525448381900787</v>
       </c>
       <c r="C28" t="n">
         <v>0.4947499930858612</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>0.4699240326881409</v>
+        <v>0.4699239432811737</v>
       </c>
       <c r="C29" t="n">
         <v>0.5137500166893005</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>0.5648236274719238</v>
+        <v>0.5648238658905029</v>
       </c>
       <c r="C30" t="n">
         <v>0.6175000071525574</v>
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>0.2616024315357208</v>
+        <v>0.261602371931076</v>
       </c>
       <c r="C32" t="n">
         <v>0.2860000133514404</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>0.2449092715978622</v>
+        <v>0.244909331202507</v>
       </c>
       <c r="C34" t="n">
         <v>0.2677499949932098</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1708191335201263</v>
+        <v>0.1708190888166428</v>
       </c>
       <c r="C36" t="n">
         <v>0.1867499947547913</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1845395117998123</v>
+        <v>0.1845395267009735</v>
       </c>
       <c r="C37" t="n">
         <v>0.2017499953508377</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1817954331636429</v>
+        <v>0.1817953586578369</v>
       </c>
       <c r="C38" t="n">
         <v>0.1987500041723251</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1893416792154312</v>
+        <v>0.1893417239189148</v>
       </c>
       <c r="C39" t="n">
         <v>0.2070000022649765</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>0.225472018122673</v>
+        <v>0.225472092628479</v>
       </c>
       <c r="C40" t="n">
         <v>0.2465000003576279</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>0.2625170946121216</v>
+        <v>0.2625171840190887</v>
       </c>
       <c r="C41" t="n">
         <v>0.2870000004768372</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>0.238506406545639</v>
+        <v>0.238506481051445</v>
       </c>
       <c r="C42" t="n">
         <v>0.2607499957084656</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>0.2581724524497986</v>
+        <v>0.2581723630428314</v>
       </c>
       <c r="C43" t="n">
         <v>0.2822499871253967</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>0.2956747710704803</v>
+        <v>0.2956749200820923</v>
       </c>
       <c r="C44" t="n">
         <v>0.3232499957084656</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3320340216159821</v>
+        <v>0.3320339620113373</v>
       </c>
       <c r="C45" t="n">
         <v>0.3630000054836273</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>0.3436963558197021</v>
+        <v>0.3436962962150574</v>
       </c>
       <c r="C46" t="n">
         <v>0.3757500052452087</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>0.2734935283660889</v>
+        <v>0.2734933793544769</v>
       </c>
       <c r="C47" t="n">
         <v>0.2989999949932098</v>
@@ -1374,7 +1386,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>0.4271620810031891</v>
+        <v>0.427162230014801</v>
       </c>
       <c r="C49" t="n">
         <v>0.4670000076293945</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>0.3519285917282104</v>
+        <v>0.3519285321235657</v>
       </c>
       <c r="C50" t="n">
         <v>0.3847500085830688</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>0.370451033115387</v>
+        <v>0.3704510629177094</v>
       </c>
       <c r="C51" t="n">
         <v>0.4050000011920929</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>0.3978919684886932</v>
+        <v>0.3978918492794037</v>
       </c>
       <c r="C52" t="n">
         <v>0.4350000023841858</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>0.3592460453510284</v>
+        <v>0.3592460751533508</v>
       </c>
       <c r="C53" t="n">
         <v>0.3927499949932098</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>0.3004769384860992</v>
+        <v>0.3004769682884216</v>
       </c>
       <c r="C54" t="n">
         <v>0.3285000026226044</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>0.2334757149219513</v>
+        <v>0.2334756553173065</v>
       </c>
       <c r="C55" t="n">
         <v>0.2552500069141388</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>0.2101509422063828</v>
+        <v>0.2101509869098663</v>
       </c>
       <c r="C56" t="n">
         <v>0.229750007390976</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>0.213352382183075</v>
+        <v>0.2133524268865585</v>
       </c>
       <c r="C57" t="n">
         <v>0.2332500070333481</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>0.2670905292034149</v>
+        <v>0.2670906484127045</v>
       </c>
       <c r="C58" t="n">
         <v>0.2919999957084656</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>0.2748654782772064</v>
+        <v>0.2748655378818512</v>
       </c>
       <c r="C59" t="n">
         <v>0.3005000054836273</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>0.311224639415741</v>
+        <v>0.3112246692180634</v>
       </c>
       <c r="C60" t="n">
         <v>0.3402499854564667</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>0.3521572351455688</v>
+        <v>0.3521571159362793</v>
       </c>
       <c r="C61" t="n">
         <v>0.3849999904632568</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>0.5469870567321777</v>
+        <v>0.5469867587089539</v>
       </c>
       <c r="C62" t="n">
         <v>0.5979999899864197</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>0.5181742310523987</v>
+        <v>0.5181741714477539</v>
       </c>
       <c r="C63" t="n">
         <v>0.5665000081062317</v>
@@ -1774,7 +1786,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1803,11 +1815,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>0.4573470950126648</v>
+        <v>0.4573468863964081</v>
       </c>
       <c r="C65" t="n">
         <v>0.5</v>
@@ -1832,11 +1844,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>0.4582616686820984</v>
+        <v>0.4582617282867432</v>
       </c>
       <c r="C66" t="n">
         <v>0.5009999871253967</v>
@@ -1861,11 +1873,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>0.3645055890083313</v>
+        <v>0.3645055592060089</v>
       </c>
       <c r="C67" t="n">
         <v>0.398499995470047</v>
@@ -1890,7 +1902,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1919,11 +1931,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>0.3043644428253174</v>
+        <v>0.3043645024299622</v>
       </c>
       <c r="C69" t="n">
         <v>0.332749992609024</v>
@@ -1948,11 +1960,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>0.2860706448554993</v>
+        <v>0.2860705256462097</v>
       </c>
       <c r="C70" t="n">
         <v>0.3127500116825104</v>
@@ -1977,11 +1989,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>0.3384367823600769</v>
+        <v>0.3384368419647217</v>
       </c>
       <c r="C71" t="n">
         <v>0.3700000047683716</v>
@@ -2006,11 +2018,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>0.3574166893959045</v>
+        <v>0.3574167490005493</v>
       </c>
       <c r="C72" t="n">
         <v>0.390749990940094</v>
@@ -2035,11 +2047,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>0.316941499710083</v>
+        <v>0.3169415891170502</v>
       </c>
       <c r="C73" t="n">
         <v>0.3465000092983246</v>
@@ -2064,11 +2076,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>0.3377507627010345</v>
+        <v>0.3377506732940674</v>
       </c>
       <c r="C74" t="n">
         <v>0.3692499995231628</v>
@@ -2093,11 +2105,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>0.3464403450489044</v>
+        <v>0.3464404046535492</v>
       </c>
       <c r="C75" t="n">
         <v>0.3787499964237213</v>
@@ -2122,11 +2134,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>0.3521572351455688</v>
+        <v>0.3521571159362793</v>
       </c>
       <c r="C76" t="n">
         <v>0.3849999904632568</v>
@@ -2151,11 +2163,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>0.2972756624221802</v>
+        <v>0.2972756028175354</v>
       </c>
       <c r="C77" t="n">
         <v>0.324999988079071</v>
@@ -2180,11 +2192,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>0.2842412292957306</v>
+        <v>0.2842411994934082</v>
       </c>
       <c r="C78" t="n">
         <v>0.3107500076293945</v>
@@ -2209,11 +2221,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3160267174243927</v>
+        <v>0.3160268068313599</v>
       </c>
       <c r="C79" t="n">
         <v>0.3454999923706055</v>
@@ -2238,11 +2250,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>0.3096239566802979</v>
+        <v>0.3096239864826202</v>
       </c>
       <c r="C80" t="n">
         <v>0.3384999930858612</v>
@@ -2267,11 +2279,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>0.3208289444446564</v>
+        <v>0.3208289742469788</v>
       </c>
       <c r="C81" t="n">
         <v>0.3507499992847443</v>
@@ -2296,11 +2308,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>0.305050402879715</v>
+        <v>0.3050504326820374</v>
       </c>
       <c r="C82" t="n">
         <v>0.3334999978542328</v>
@@ -2325,11 +2337,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>0.2739508748054504</v>
+        <v>0.2739508450031281</v>
       </c>
       <c r="C83" t="n">
         <v>0.2994999885559082</v>
@@ -2354,11 +2366,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>0.2754881680011749</v>
+        <v>0.2754880487918854</v>
       </c>
       <c r="C84" t="n">
         <v>0.2992500066757202</v>
@@ -2383,11 +2395,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>0.2821624577045441</v>
+        <v>0.2821623682975769</v>
       </c>
       <c r="C85" t="n">
         <v>0.3064999878406525</v>
@@ -2412,11 +2424,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>0.2821624577045441</v>
+        <v>0.2821623682975769</v>
       </c>
       <c r="C86" t="n">
         <v>0.3064999878406525</v>
@@ -2441,11 +2453,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>0.2931558787822723</v>
+        <v>0.2931559085845947</v>
       </c>
       <c r="C87" t="n">
         <v>0.3165000081062317</v>
@@ -2470,11 +2482,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>0.297092467546463</v>
+        <v>0.2970925867557526</v>
       </c>
       <c r="C88" t="n">
         <v>0.3207499980926514</v>
@@ -2499,11 +2511,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>0.3188591599464417</v>
+        <v>0.3188592195510864</v>
       </c>
       <c r="C89" t="n">
         <v>0.3442499935626984</v>
@@ -2528,7 +2540,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2557,11 +2569,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>0.3267626464366913</v>
+        <v>0.3267627358436584</v>
       </c>
       <c r="C91" t="n">
         <v>0.3510000109672546</v>
@@ -2586,11 +2598,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>0.3360722959041595</v>
+        <v>0.33607217669487</v>
       </c>
       <c r="C92" t="n">
         <v>0.3610000014305115</v>
@@ -2615,11 +2627,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>0.3450179696083069</v>
+        <v>0.3450179100036621</v>
       </c>
       <c r="C93" t="n">
         <v>0.3687500059604645</v>
@@ -2644,11 +2656,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>0.3639646172523499</v>
+        <v>0.3639647960662842</v>
       </c>
       <c r="C94" t="n">
         <v>0.3889999985694885</v>
@@ -2673,11 +2685,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>0.3553100824356079</v>
+        <v>0.3553100526332855</v>
       </c>
       <c r="C95" t="n">
         <v>0.3797500133514404</v>
@@ -2702,11 +2714,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>0.3668766617774963</v>
+        <v>0.3668765723705292</v>
       </c>
       <c r="C96" t="n">
         <v>0.3899999856948853</v>
@@ -2731,11 +2743,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>0.3767540752887726</v>
+        <v>0.3767539262771606</v>
       </c>
       <c r="C97" t="n">
         <v>0.4004999995231628</v>
@@ -2760,11 +2772,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>0.3692283630371094</v>
+        <v>0.3692283034324646</v>
       </c>
       <c r="C98" t="n">
         <v>0.3925000131130219</v>
@@ -2789,11 +2801,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>0.4342075288295746</v>
+        <v>0.4342076480388641</v>
       </c>
       <c r="C99" t="n">
         <v>0.4595000147819519</v>
@@ -2818,11 +2830,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>0.42310431599617</v>
+        <v>0.4231043457984924</v>
       </c>
       <c r="C100" t="n">
         <v>0.4477500021457672</v>
@@ -2847,11 +2859,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>0.4363338053226471</v>
+        <v>0.4363337159156799</v>
       </c>
       <c r="C101" t="n">
         <v>0.4617500007152557</v>
@@ -2876,11 +2888,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>0.4509218335151672</v>
+        <v>0.4509216248989105</v>
       </c>
       <c r="C102" t="n">
         <v>0.4749999940395355</v>
@@ -2905,11 +2917,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>0.4400046467781067</v>
+        <v>0.4400047361850739</v>
       </c>
       <c r="C103" t="n">
         <v>0.4634999930858612</v>
@@ -2934,11 +2946,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>0.4153226315975189</v>
+        <v>0.4153225719928741</v>
       </c>
       <c r="C104" t="n">
         <v>0.4375</v>
@@ -2963,11 +2975,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>0.4636435508728027</v>
+        <v>0.4636434316635132</v>
       </c>
       <c r="C105" t="n">
         <v>0.4862500131130219</v>
@@ -2992,11 +3004,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>0.4398057460784912</v>
+        <v>0.4398057162761688</v>
       </c>
       <c r="C106" t="n">
         <v>0.4612500071525574</v>
@@ -3021,11 +3033,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>0.4657888114452362</v>
+        <v>0.4657887816429138</v>
       </c>
       <c r="C107" t="n">
         <v>0.4884999990463257</v>
@@ -3050,11 +3062,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>0.5019922256469727</v>
+        <v>0.5019922852516174</v>
       </c>
       <c r="C108" t="n">
         <v>0.5242499709129333</v>
@@ -3079,11 +3091,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>0.4799687564373016</v>
+        <v>0.4799687266349792</v>
       </c>
       <c r="C109" t="n">
         <v>0.5012500286102295</v>
@@ -3108,11 +3120,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>0.4596208930015564</v>
+        <v>0.4596209228038788</v>
       </c>
       <c r="C110" t="n">
         <v>0.4799999892711639</v>
@@ -3137,11 +3149,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>0.5301187634468079</v>
+        <v>0.5301188826560974</v>
       </c>
       <c r="C111" t="n">
         <v>0.5515000224113464</v>
@@ -3166,11 +3178,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>0.5029637813568115</v>
+        <v>0.5029641389846802</v>
       </c>
       <c r="C112" t="n">
         <v>0.5232499837875366</v>
@@ -3195,11 +3207,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>0.5334832072257996</v>
+        <v>0.5334831476211548</v>
       </c>
       <c r="C113" t="n">
         <v>0.5550000071525574</v>
@@ -3224,11 +3236,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>0.5342625975608826</v>
+        <v>0.5342623591423035</v>
       </c>
       <c r="C114" t="n">
         <v>0.5532500147819519</v>
@@ -3253,11 +3265,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>0.485495537519455</v>
+        <v>0.4854955673217773</v>
       </c>
       <c r="C115" t="n">
         <v>0.5027499794960022</v>
@@ -3282,11 +3294,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>0.4816328585147858</v>
+        <v>0.4816329181194305</v>
       </c>
       <c r="C116" t="n">
         <v>0.4987500011920929</v>
@@ -3311,7 +3323,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3340,11 +3352,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>0.5976042151451111</v>
+        <v>0.5976039171218872</v>
       </c>
       <c r="C118" t="n">
         <v>0.6162499785423279</v>
@@ -3369,11 +3381,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>0.6877905130386353</v>
+        <v>0.6877904534339905</v>
       </c>
       <c r="C119" t="n">
         <v>0.7092499732971191</v>
@@ -3398,11 +3410,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>0.7719261646270752</v>
+        <v>0.7719263434410095</v>
       </c>
       <c r="C120" t="n">
         <v>0.7929999828338623</v>
@@ -3427,11 +3439,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>0.8021026253700256</v>
+        <v>0.8021024465560913</v>
       </c>
       <c r="C121" t="n">
         <v>0.8240000009536743</v>
@@ -3456,11 +3468,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>0.7127906084060669</v>
+        <v>0.7127904891967773</v>
       </c>
       <c r="C122" t="n">
         <v>0.7322499752044678</v>
@@ -3485,11 +3497,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>0.7659459710121155</v>
+        <v>0.7659459114074707</v>
       </c>
       <c r="C123" t="n">
         <v>0.7839999794960022</v>
@@ -3514,11 +3526,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>0.8702375292778015</v>
+        <v>0.8702377080917358</v>
       </c>
       <c r="C124" t="n">
         <v>0.890749990940094</v>
@@ -3543,7 +3555,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3572,11 +3584,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>1.144066333770752</v>
+        <v>1.144066214561462</v>
       </c>
       <c r="C126" t="n">
         <v>1.167999982833862</v>
@@ -3601,11 +3613,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>1.151167869567871</v>
+        <v>1.151167750358582</v>
       </c>
       <c r="C127" t="n">
         <v>1.175250053405762</v>
@@ -3630,11 +3642,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>1.398248553276062</v>
+        <v>1.39824903011322</v>
       </c>
       <c r="C128" t="n">
         <v>1.427500009536743</v>
@@ -3659,11 +3671,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>1.504844546318054</v>
+        <v>1.504844427108765</v>
       </c>
       <c r="C129" t="n">
         <v>1.533499956130981</v>
@@ -3688,11 +3700,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>1.68099057674408</v>
+        <v>1.68099045753479</v>
       </c>
       <c r="C130" t="n">
         <v>1.713000059127808</v>
@@ -3717,7 +3729,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3746,11 +3758,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>2.265316009521484</v>
+        <v>2.265315294265747</v>
       </c>
       <c r="C132" t="n">
         <v>2.305000066757202</v>
@@ -3775,11 +3787,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>2.622556686401367</v>
+        <v>2.622555732727051</v>
       </c>
       <c r="C133" t="n">
         <v>2.668499946594238</v>
@@ -3804,7 +3816,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3833,11 +3845,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>2.496467351913452</v>
+        <v>2.496467113494873</v>
       </c>
       <c r="C135" t="n">
         <v>2.536999940872192</v>
@@ -3862,11 +3874,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>2.679741144180298</v>
+        <v>2.679741621017456</v>
       </c>
       <c r="C136" t="n">
         <v>2.723249912261963</v>
@@ -3891,11 +3903,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>2.565840721130371</v>
+        <v>2.56584095954895</v>
       </c>
       <c r="C137" t="n">
         <v>2.607500076293945</v>
@@ -3920,11 +3932,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>3.554835081100464</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="C138" t="n">
         <v>3.608750104904175</v>
@@ -3949,11 +3961,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>3.56000542640686</v>
+        <v>3.560006141662598</v>
       </c>
       <c r="C139" t="n">
         <v>3.614000082015991</v>
@@ -3978,11 +3990,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>4.002049446105957</v>
+        <v>4.00205135345459</v>
       </c>
       <c r="C140" t="n">
         <v>4.062749862670898</v>
@@ -4007,11 +4019,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>4.176386833190918</v>
+        <v>4.17638635635376</v>
       </c>
       <c r="C141" t="n">
         <v>4.236000061035156</v>
@@ -4036,7 +4048,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4065,11 +4077,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>5.097487926483154</v>
+        <v>5.097489833831787</v>
       </c>
       <c r="C143" t="n">
         <v>5.170249938964844</v>
@@ -4094,11 +4106,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>4.950572490692139</v>
+        <v>4.95057201385498</v>
       </c>
       <c r="C144" t="n">
         <v>5.017749786376953</v>
@@ -4123,11 +4135,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>4.772733688354492</v>
+        <v>4.772735118865967</v>
       </c>
       <c r="C145" t="n">
         <v>4.837500095367432</v>
@@ -4152,7 +4164,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4181,11 +4193,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>5.972711086273193</v>
+        <v>5.972710609436035</v>
       </c>
       <c r="C147" t="n">
         <v>6.050000190734863</v>
@@ -4210,11 +4222,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>5.715786457061768</v>
+        <v>5.715786933898926</v>
       </c>
       <c r="C148" t="n">
         <v>5.789750099182129</v>
@@ -4239,7 +4251,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4268,11 +4280,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>6.22805643081665</v>
+        <v>6.228057861328125</v>
       </c>
       <c r="C150" t="n">
         <v>6.304749965667725</v>
@@ -4297,11 +4309,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>5.850456714630127</v>
+        <v>5.850456237792969</v>
       </c>
       <c r="C151" t="n">
         <v>5.922500133514404</v>
@@ -4326,7 +4338,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4355,11 +4367,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>6.935434818267822</v>
+        <v>6.935435771942139</v>
       </c>
       <c r="C153" t="n">
         <v>7.017000198364258</v>
@@ -4384,11 +4396,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>6.943834781646729</v>
+        <v>6.94383430480957</v>
       </c>
       <c r="C154" t="n">
         <v>7.025499820709229</v>
@@ -4413,11 +4425,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>5.209483623504639</v>
+        <v>5.209482192993164</v>
       </c>
       <c r="C155" t="n">
         <v>5.270750045776367</v>
@@ -4442,7 +4454,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4471,11 +4483,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>3.302005290985107</v>
+        <v>3.302005529403687</v>
       </c>
       <c r="C157" t="n">
         <v>3.337500095367432</v>
@@ -4500,11 +4512,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>3.555529356002808</v>
+        <v>3.555529594421387</v>
       </c>
       <c r="C158" t="n">
         <v>3.59375</v>
@@ -4529,11 +4541,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>3.819418668746948</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="C159" t="n">
         <v>3.856499910354614</v>
@@ -4558,7 +4570,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4587,7 +4599,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4616,11 +4628,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>3.357765197753906</v>
+        <v>3.357765674591064</v>
       </c>
       <c r="C162" t="n">
         <v>3.386499881744385</v>
@@ -4645,11 +4657,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>4.070913791656494</v>
+        <v>4.070912837982178</v>
       </c>
       <c r="C163" t="n">
         <v>4.10575008392334</v>
@@ -4674,11 +4686,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>4.182210922241211</v>
+        <v>4.182210445404053</v>
       </c>
       <c r="C164" t="n">
         <v>4.217999935150146</v>
@@ -4703,7 +4715,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4732,11 +4744,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>4.319095611572266</v>
+        <v>4.31909704208374</v>
       </c>
       <c r="C166" t="n">
         <v>4.351749897003174</v>
@@ -4761,11 +4773,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>4.987792491912842</v>
+        <v>4.987791061401367</v>
       </c>
       <c r="C167" t="n">
         <v>5.025499820709229</v>
@@ -4790,11 +4802,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>5.381809234619141</v>
+        <v>5.381809711456299</v>
       </c>
       <c r="C168" t="n">
         <v>5.418499946594238</v>
@@ -4819,11 +4831,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>5.842669010162354</v>
+        <v>5.842668533325195</v>
       </c>
       <c r="C169" t="n">
         <v>5.882500171661377</v>
@@ -4848,11 +4860,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>5.870727062225342</v>
+        <v>5.870725154876709</v>
       </c>
       <c r="C170" t="n">
         <v>5.910749912261963</v>
@@ -4877,7 +4889,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4906,11 +4918,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>6.549292087554932</v>
+        <v>6.549293041229248</v>
       </c>
       <c r="C172" t="n">
         <v>6.590000152587891</v>
@@ -4935,11 +4947,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>7.261862277984619</v>
+        <v>7.261863708496094</v>
       </c>
       <c r="C173" t="n">
         <v>7.307000160217285</v>
@@ -4964,11 +4976,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>8.820674896240234</v>
+        <v>8.820673942565918</v>
       </c>
       <c r="C174" t="n">
         <v>8.875499725341797</v>
@@ -4993,11 +5005,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>9.443390846252441</v>
+        <v>9.443389892578125</v>
       </c>
       <c r="C175" t="n">
         <v>9.497750282287598</v>
@@ -5022,11 +5034,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>10.55399608612061</v>
+        <v>10.55399417877197</v>
       </c>
       <c r="C176" t="n">
         <v>10.61474990844727</v>
@@ -5051,11 +5063,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>13.29794979095459</v>
+        <v>13.29795074462891</v>
       </c>
       <c r="C177" t="n">
         <v>13.3745002746582</v>
@@ -5080,7 +5092,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5109,7 +5121,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5138,7 +5150,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5167,11 +5179,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>12.98799610137939</v>
+        <v>12.98799991607666</v>
       </c>
       <c r="C181" t="n">
         <v>13.05500030517578</v>
@@ -5196,11 +5208,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>12.92308330535889</v>
+        <v>12.92308044433594</v>
       </c>
       <c r="C182" t="n">
         <v>12.98974990844727</v>
@@ -5225,11 +5237,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>13.6441125869751</v>
+        <v>13.64411449432373</v>
       </c>
       <c r="C183" t="n">
         <v>13.71450042724609</v>
@@ -5254,11 +5266,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>13.28432750701904</v>
+        <v>13.28432464599609</v>
       </c>
       <c r="C184" t="n">
         <v>13.34825038909912</v>
@@ -5283,11 +5295,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>14.93762016296387</v>
+        <v>14.93761920928955</v>
       </c>
       <c r="C185" t="n">
         <v>15.00949954986572</v>
@@ -5312,11 +5324,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>16.16670227050781</v>
+        <v>16.16670799255371</v>
       </c>
       <c r="C186" t="n">
         <v>16.24449920654297</v>
@@ -5341,11 +5353,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>19.9112720489502</v>
+        <v>19.91127395629883</v>
       </c>
       <c r="C187" t="n">
         <v>20.00250053405762</v>
@@ -5370,11 +5382,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>19.41007423400879</v>
+        <v>19.41006851196289</v>
       </c>
       <c r="C188" t="n">
         <v>19.49900054931641</v>
@@ -5399,11 +5411,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>22.28682899475098</v>
+        <v>22.28683853149414</v>
       </c>
       <c r="C189" t="n">
         <v>22.38500022888184</v>
@@ -5428,11 +5440,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>20.62515258789062</v>
+        <v>20.62515449523926</v>
       </c>
       <c r="C190" t="n">
         <v>20.71599960327148</v>
@@ -5457,11 +5469,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>25.45488166809082</v>
+        <v>25.45487785339355</v>
       </c>
       <c r="C191" t="n">
         <v>25.5669994354248</v>
@@ -5486,11 +5498,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>32.53271102905273</v>
+        <v>32.5327033996582</v>
       </c>
       <c r="C192" t="n">
         <v>32.67599868774414</v>
@@ -5515,11 +5527,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>29.28561401367188</v>
+        <v>29.28561019897461</v>
       </c>
       <c r="C193" t="n">
         <v>29.4109992980957</v>
@@ -5544,11 +5556,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>24.38160705566406</v>
+        <v>24.3816032409668</v>
       </c>
       <c r="C194" t="n">
         <v>24.48600006103516</v>
@@ -5573,7 +5585,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5602,7 +5614,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5631,7 +5643,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5660,11 +5672,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>18.5955638885498</v>
+        <v>18.59556579589844</v>
       </c>
       <c r="C198" t="n">
         <v>18.67200088500977</v>
@@ -5689,11 +5701,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>15.10013771057129</v>
+        <v>15.10013675689697</v>
       </c>
       <c r="C199" t="n">
         <v>15.15900039672852</v>
@@ -5718,7 +5730,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5747,11 +5759,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>15.03538608551025</v>
+        <v>15.03538703918457</v>
       </c>
       <c r="C201" t="n">
         <v>15.0939998626709</v>
@@ -5776,11 +5788,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>12.09545516967773</v>
+        <v>12.09545421600342</v>
       </c>
       <c r="C202" t="n">
         <v>12.13899993896484</v>
@@ -5805,11 +5817,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>13.44858264923096</v>
+        <v>13.44858169555664</v>
       </c>
       <c r="C203" t="n">
         <v>13.49699974060059</v>
@@ -5834,11 +5846,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>16.86660957336426</v>
+        <v>16.86660385131836</v>
       </c>
       <c r="C204" t="n">
         <v>16.92300033569336</v>
@@ -5863,11 +5875,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>14.56530094146729</v>
+        <v>14.5653018951416</v>
       </c>
       <c r="C205" t="n">
         <v>14.61400032043457</v>
@@ -5892,11 +5904,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>19.47189903259277</v>
+        <v>19.47190093994141</v>
       </c>
       <c r="C206" t="n">
         <v>19.53700065612793</v>
@@ -5921,7 +5933,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5950,11 +5962,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>27.68914222717285</v>
+        <v>27.68914413452148</v>
       </c>
       <c r="C208" t="n">
         <v>27.77700042724609</v>
@@ -5979,7 +5991,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6008,7 +6020,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6037,11 +6049,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>42.17256546020508</v>
+        <v>42.17256164550781</v>
       </c>
       <c r="C211" t="n">
         <v>42.30199813842773</v>
@@ -6066,11 +6078,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>46.58600997924805</v>
+        <v>46.58601379394531</v>
       </c>
       <c r="C212" t="n">
         <v>46.72900009155273</v>
@@ -6095,7 +6107,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6124,11 +6136,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>43.36947250366211</v>
+        <v>43.36948013305664</v>
       </c>
       <c r="C214" t="n">
         <v>43.49900054931641</v>
@@ -6153,11 +6165,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>40.65856552124023</v>
+        <v>40.6585693359375</v>
       </c>
       <c r="C215" t="n">
         <v>40.77999877929688</v>
@@ -6182,11 +6194,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>46.63073348999023</v>
+        <v>46.6307373046875</v>
       </c>
       <c r="C216" t="n">
         <v>46.77000045776367</v>
@@ -6211,11 +6223,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>49.37887954711914</v>
+        <v>49.37887573242188</v>
       </c>
       <c r="C217" t="n">
         <v>49.52199935913086</v>
@@ -6240,11 +6252,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>61.34918975830078</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="C218" t="n">
         <v>61.52700042724609</v>
@@ -6269,7 +6281,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6298,11 +6310,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>90.09910583496094</v>
+        <v>90.09909820556641</v>
       </c>
       <c r="C220" t="n">
         <v>90.35600280761719</v>
@@ -6327,11 +6339,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>86.15633392333984</v>
+        <v>86.15634155273438</v>
       </c>
       <c r="C221" t="n">
         <v>86.40200042724609</v>
@@ -6356,7 +6368,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6385,11 +6397,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>123.198860168457</v>
+        <v>123.1988525390625</v>
       </c>
       <c r="C223" t="n">
         <v>123.5400009155273</v>
@@ -6414,11 +6426,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>116.6968536376953</v>
+        <v>116.6968688964844</v>
       </c>
       <c r="C224" t="n">
         <v>117.0199966430664</v>
@@ -6443,7 +6455,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6472,7 +6484,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6501,7 +6513,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6530,7 +6542,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6559,11 +6571,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>133.9398803710938</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="C229" t="n">
         <v>134.2899932861328</v>
@@ -6588,7 +6600,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6617,11 +6629,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>124.5942916870117</v>
+        <v>124.5942840576172</v>
       </c>
       <c r="C231" t="n">
         <v>124.9199981689453</v>
@@ -6646,11 +6658,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>108.1073608398438</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="C232" t="n">
         <v>108.379997253418</v>
@@ -6675,7 +6687,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6704,11 +6716,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>134.7901000976562</v>
+        <v>134.7900695800781</v>
       </c>
       <c r="C234" t="n">
         <v>135.1300048828125</v>
@@ -6733,11 +6745,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>157.603515625</v>
+        <v>157.6035308837891</v>
       </c>
       <c r="C235" t="n">
         <v>157.9900054931641</v>
@@ -6762,11 +6774,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>177.4348602294922</v>
+        <v>177.4348754882812</v>
       </c>
       <c r="C236" t="n">
         <v>177.8699951171875</v>
@@ -6791,11 +6803,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>173.7538757324219</v>
+        <v>173.75390625</v>
       </c>
       <c r="C237" t="n">
         <v>174.1799926757812</v>
@@ -6820,11 +6832,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>186.1340484619141</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="C238" t="n">
         <v>186.5800018310547</v>
@@ -6849,11 +6861,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="C239" t="n">
         <v>202.4900054931641</v>
@@ -6878,7 +6890,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6907,11 +6919,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>186.0646209716797</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="C241" t="n">
         <v>186.5</v>
@@ -6936,7 +6948,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6965,7 +6977,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6994,11 +7006,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="C244" t="n">
         <v>174.3999938964844</v>
@@ -7023,11 +7035,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="C245" t="n">
         <v>199.5700073242188</v>
@@ -7052,7 +7064,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7081,7 +7093,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7110,7 +7122,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7139,7 +7151,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7168,32 +7180,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>225.5099945068359</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="C250" t="n">
-        <v>225.5099945068359</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="D250" t="n">
-        <v>1833872800</v>
+        <v>1911418600</v>
       </c>
       <c r="E250" t="n">
         <v>7.910000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>28.50948097431554</v>
+        <v>28.39190920746582</v>
       </c>
       <c r="G250" t="n">
         <v>24100000000</v>
       </c>
       <c r="H250" t="n">
-        <v>5434790867614.746</v>
+        <v>5412378044128.418</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07609430705394191</v>
+        <v>0.07931197510373444</v>
       </c>
     </row>
   </sheetData>
@@ -7225,75 +7237,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39565</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39656</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40045</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7329,13 +7341,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39657</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39747</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40136</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7371,13 +7383,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39839</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39929</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40319</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7413,13 +7425,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39930</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40020</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40045</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7455,13 +7467,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40021</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40111</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40136</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7497,13 +7509,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40112</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40618</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7530,7 +7542,7 @@
       <c r="I7" t="n">
         <v>-0.003499999999999998</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40618</v>
       </c>
       <c r="K7" t="n">
@@ -7543,13 +7555,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40300</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40319</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7576,7 +7588,7 @@
       <c r="I8" t="n">
         <v>0.0115</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40618</v>
       </c>
       <c r="K8" t="n">
@@ -7589,13 +7601,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40301</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40420</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7622,7 +7634,7 @@
       <c r="I9" t="n">
         <v>0.01</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40618</v>
       </c>
       <c r="K9" t="n">
@@ -7635,13 +7647,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40392</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40519</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7668,7 +7680,7 @@
       <c r="I10" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40618</v>
       </c>
       <c r="K10" t="n">
@@ -7681,13 +7693,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40573</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40618</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7714,7 +7726,7 @@
       <c r="I11" t="n">
         <v>0.0105</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40618</v>
       </c>
       <c r="K11" t="n">
@@ -7727,13 +7739,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40690</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7760,7 +7772,7 @@
       <c r="I12" t="n">
         <v>0.01025</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40690</v>
       </c>
       <c r="K12" t="n">
@@ -7773,13 +7785,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40665</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40780</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7806,7 +7818,7 @@
       <c r="I13" t="n">
         <v>0.02275</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40780</v>
       </c>
       <c r="K13" t="n">
@@ -7819,13 +7831,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40846</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7852,7 +7864,7 @@
       <c r="I14" t="n">
         <v>0.02625</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="K14" t="n">
@@ -7865,13 +7877,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40937</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40981</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7898,7 +7910,7 @@
       <c r="I15" t="n">
         <v>0.02375</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40981</v>
       </c>
       <c r="K15" t="n">
@@ -7911,13 +7923,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40938</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41028</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41052</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7944,7 +7956,7 @@
       <c r="I16" t="n">
         <v>0.02075</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41052</v>
       </c>
       <c r="K16" t="n">
@@ -7957,13 +7969,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41119</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41143</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7990,7 +8002,7 @@
       <c r="I17" t="n">
         <v>0.01925</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41143</v>
       </c>
       <c r="K17" t="n">
@@ -8003,13 +8015,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41120</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41210</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41232</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8036,7 +8048,7 @@
       <c r="I18" t="n">
         <v>0.02025</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41232</v>
       </c>
       <c r="K18" t="n">
@@ -8049,13 +8061,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41211</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41301</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41345</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8082,7 +8094,7 @@
       <c r="I19" t="n">
         <v>0.0225</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41345</v>
       </c>
       <c r="K19" t="n">
@@ -8095,13 +8107,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41302</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41392</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41416</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8128,7 +8140,7 @@
       <c r="I20" t="n">
         <v>0.02325</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41416</v>
       </c>
       <c r="K20" t="n">
@@ -8141,13 +8153,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41393</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41483</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41507</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8174,7 +8186,7 @@
       <c r="I21" t="n">
         <v>0.0225</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41507</v>
       </c>
       <c r="K21" t="n">
@@ -8187,13 +8199,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41484</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41574</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41597</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8220,7 +8232,7 @@
       <c r="I22" t="n">
         <v>0.01925</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41597</v>
       </c>
       <c r="K22" t="n">
@@ -8233,13 +8245,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41575</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41665</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41711</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8266,7 +8278,7 @@
       <c r="I23" t="n">
         <v>0.0185</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41711</v>
       </c>
       <c r="K23" t="n">
@@ -8279,13 +8291,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41666</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41756</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41780</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8312,7 +8324,7 @@
       <c r="I24" t="n">
         <v>0.02125</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41780</v>
       </c>
       <c r="K24" t="n">
@@ -8325,13 +8337,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41757</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41847</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41871</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8358,7 +8370,7 @@
       <c r="I25" t="n">
         <v>0.02275</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41871</v>
       </c>
       <c r="K25" t="n">
@@ -8371,13 +8383,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41848</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41938</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41962</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8404,7 +8416,7 @@
       <c r="I26" t="n">
         <v>0.0255</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41962</v>
       </c>
       <c r="K26" t="n">
@@ -8417,13 +8429,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41939</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42029</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42075</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8450,7 +8462,7 @@
       <c r="I27" t="n">
         <v>0.028</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42075</v>
       </c>
       <c r="K27" t="n">
@@ -8463,13 +8475,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42030</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42120</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42144</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8496,7 +8508,7 @@
       <c r="I28" t="n">
         <v>0.028</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42144</v>
       </c>
       <c r="K28" t="n">
@@ -8509,13 +8521,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42121</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42211</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42235</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8542,7 +8554,7 @@
       <c r="I29" t="n">
         <v>0.02375</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42235</v>
       </c>
       <c r="K29" t="n">
@@ -8555,13 +8567,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42212</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42302</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42326</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8588,7 +8600,7 @@
       <c r="I30" t="n">
         <v>0.027</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42326</v>
       </c>
       <c r="K30" t="n">
@@ -8601,13 +8613,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42303</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42446</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8634,7 +8646,7 @@
       <c r="I31" t="n">
         <v>0.027</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42446</v>
       </c>
       <c r="K31" t="n">
@@ -8647,13 +8659,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42515</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8680,7 +8692,7 @@
       <c r="I32" t="n">
         <v>0.02925</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42515</v>
       </c>
       <c r="K32" t="n">
@@ -8693,13 +8705,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42492</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42605</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8726,7 +8738,7 @@
       <c r="I33" t="n">
         <v>0.038</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42605</v>
       </c>
       <c r="K33" t="n">
@@ -8739,13 +8751,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42673</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8772,7 +8784,7 @@
       <c r="I34" t="n">
         <v>0.04775</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="K34" t="n">
@@ -8785,13 +8797,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42764</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8818,7 +8830,7 @@
       <c r="I35" t="n">
         <v>0.06375</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="K35" t="n">
@@ -8831,13 +8843,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42765</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8864,7 +8876,7 @@
       <c r="I36" t="n">
         <v>0.07525</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="K36" t="n">
@@ -8877,13 +8889,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42946</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42970</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8910,7 +8922,7 @@
       <c r="I37" t="n">
         <v>0.08825</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42970</v>
       </c>
       <c r="K37" t="n">
@@ -8923,13 +8935,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43037</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43060</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8956,7 +8968,7 @@
       <c r="I38" t="n">
         <v>0.10075</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43060</v>
       </c>
       <c r="K38" t="n">
@@ -8969,13 +8981,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43038</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43128</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9002,7 +9014,7 @@
       <c r="I39" t="n">
         <v>0.1205</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="K39" t="n">
@@ -9015,13 +9027,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43129</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43219</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9048,7 +9060,7 @@
       <c r="I40" t="n">
         <v>0.15025</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="K40" t="n">
@@ -9061,13 +9073,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43310</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43328</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9094,7 +9106,7 @@
       <c r="I41" t="n">
         <v>0.17125</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43328</v>
       </c>
       <c r="K41" t="n">
@@ -9107,13 +9119,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43311</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43401</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43419</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9140,7 +9152,7 @@
       <c r="I42" t="n">
         <v>0.18725</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43419</v>
       </c>
       <c r="K42" t="n">
@@ -9153,13 +9165,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43402</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43492</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9186,7 +9198,7 @@
       <c r="I43" t="n">
         <v>0.16575</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K43" t="n">
@@ -9199,13 +9211,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43493</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43583</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43601</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9232,7 +9244,7 @@
       <c r="I44" t="n">
         <v>0.13225</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43601</v>
       </c>
       <c r="K44" t="n">
@@ -9245,13 +9257,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43584</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43674</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43692</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9278,7 +9290,7 @@
       <c r="I45" t="n">
         <v>0.11075</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43692</v>
       </c>
       <c r="K45" t="n">
@@ -9291,13 +9303,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43675</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43765</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43783</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9324,7 +9336,7 @@
       <c r="I46" t="n">
         <v>0.09775</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43783</v>
       </c>
       <c r="K46" t="n">
@@ -9337,13 +9349,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43766</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43856</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9370,7 +9382,7 @@
       <c r="I47" t="n">
         <v>0.113</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K47" t="n">
@@ -9383,13 +9395,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43857</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43947</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9416,7 +9428,7 @@
       <c r="I48" t="n">
         <v>0.13375</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="K48" t="n">
@@ -9429,13 +9441,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43948</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44038</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44062</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9462,7 +9474,7 @@
       <c r="I49" t="n">
         <v>0.136</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44062</v>
       </c>
       <c r="K49" t="n">
@@ -9475,13 +9487,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44129</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44153</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9508,7 +9520,7 @@
       <c r="I50" t="n">
         <v>0.15275</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44153</v>
       </c>
       <c r="K50" t="n">
@@ -9521,13 +9533,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44130</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9554,7 +9566,7 @@
       <c r="I51" t="n">
         <v>0.1725</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="K51" t="n">
@@ -9567,13 +9579,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44318</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44342</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9600,7 +9612,7 @@
       <c r="I52" t="n">
         <v>0.2115</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44342</v>
       </c>
       <c r="K52" t="n">
@@ -9613,13 +9625,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44319</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9646,7 +9658,7 @@
       <c r="I53" t="n">
         <v>0.28075</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="K53" t="n">
@@ -9659,13 +9671,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44410</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44522</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9692,7 +9704,7 @@
       <c r="I54" t="n">
         <v>0.32475</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44522</v>
       </c>
       <c r="K54" t="n">
@@ -9705,13 +9717,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9738,7 +9750,7 @@
       <c r="I55" t="n">
         <v>0.385</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="K55" t="n">
@@ -9751,13 +9763,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9784,7 +9796,7 @@
       <c r="I56" t="n">
         <v>0.37325</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="K56" t="n">
@@ -9797,13 +9809,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44683</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9830,7 +9842,7 @@
       <c r="I57" t="n">
         <v>0.30525</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="K57" t="n">
@@ -9843,13 +9855,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44864</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9876,7 +9888,7 @@
       <c r="I58" t="n">
         <v>0.23525</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="K58" t="n">
@@ -9889,13 +9901,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9922,7 +9934,7 @@
       <c r="I59" t="n">
         <v>0.174</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="K59" t="n">
@@ -9935,13 +9947,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44956</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9968,7 +9980,7 @@
       <c r="I60" t="n">
         <v>0.192</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="K60" t="n">
@@ -9981,13 +9993,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45137</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45166</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10014,7 +10026,7 @@
       <c r="I61" t="n">
         <v>0.414</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45166</v>
       </c>
       <c r="K61" t="n">
@@ -10027,13 +10039,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45228</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10060,7 +10072,7 @@
       <c r="I62" t="n">
         <v>0.758</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="K62" t="n">
@@ -10073,13 +10085,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45319</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10106,7 +10118,7 @@
       <c r="I63" t="n">
         <v>1.193</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="K63" t="n">
@@ -10119,13 +10131,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45320</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45410</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45441</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10152,7 +10164,7 @@
       <c r="I64" t="n">
         <v>1.709</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45441</v>
       </c>
       <c r="K64" t="n">
@@ -10165,13 +10177,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45501</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45532</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10198,7 +10210,7 @@
       <c r="I65" t="n">
         <v>2.131</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45532</v>
       </c>
       <c r="K65" t="n">
@@ -10211,13 +10223,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45502</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45592</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45616</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10244,7 +10256,7 @@
       <c r="I66" t="n">
         <v>2.54</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45616</v>
       </c>
       <c r="K66" t="n">
@@ -10257,13 +10269,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45593</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45683</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10290,7 +10302,7 @@
       <c r="I67" t="n">
         <v>2.94</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="K67" t="n">
@@ -10303,13 +10315,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45684</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45774</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10336,7 +10348,7 @@
       <c r="I68" t="n">
         <v>3.102</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="K68" t="n">
@@ -10349,13 +10361,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45775</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45865</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10382,7 +10394,7 @@
       <c r="I69" t="n">
         <v>3.512</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="K69" t="n">
@@ -10395,13 +10407,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45866</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45956</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45980</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10428,7 +10440,7 @@
       <c r="I70" t="n">
         <v>4.032</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45980</v>
       </c>
       <c r="K70" t="n">
@@ -10441,13 +10453,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45957</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46047</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10474,7 +10486,7 @@
       <c r="I71" t="n">
         <v>4.9</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="K71" t="n">
@@ -10487,13 +10499,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46048</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46162</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10520,7 +10532,7 @@
       <c r="I72" t="n">
         <v>6.530000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46162</v>
       </c>
       <c r="K72" t="n">
@@ -10533,13 +10545,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46229</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46260</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10566,7 +10578,7 @@
       <c r="I73" t="n">
         <v>7.910000000000001</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46260</v>
       </c>
       <c r="K73" t="n">
@@ -10603,52 +10615,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40042</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40045</v>
       </c>
       <c r="C2" t="n">
@@ -10677,10 +10689,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40134</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40136</v>
       </c>
       <c r="C3" t="n">
@@ -10709,10 +10721,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40247</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40255</v>
       </c>
       <c r="C4" t="n">
@@ -10741,10 +10753,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40315</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40319</v>
       </c>
       <c r="C5" t="n">
@@ -10773,10 +10785,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40415</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40420</v>
       </c>
       <c r="C6" t="n">
@@ -10805,10 +10817,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40500</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40519</v>
       </c>
       <c r="C7" t="n">
@@ -10837,10 +10849,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40612</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40618</v>
       </c>
       <c r="C8" t="n">
@@ -10869,10 +10881,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40686</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40690</v>
       </c>
       <c r="C9" t="n">
@@ -10901,10 +10913,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40774</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40780</v>
       </c>
       <c r="C10" t="n">
@@ -10933,10 +10945,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40864</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40869</v>
       </c>
       <c r="C11" t="n">
@@ -10965,10 +10977,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40977</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40981</v>
       </c>
       <c r="C12" t="n">
@@ -10997,10 +11009,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41047</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41052</v>
       </c>
       <c r="C13" t="n">
@@ -11029,10 +11041,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41138</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41143</v>
       </c>
       <c r="C14" t="n">
@@ -11061,10 +11073,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41229</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41232</v>
       </c>
       <c r="C15" t="n">
@@ -11093,10 +11105,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41341</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41345</v>
       </c>
       <c r="C16" t="n">
@@ -11125,10 +11137,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41411</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41416</v>
       </c>
       <c r="C17" t="n">
@@ -11157,10 +11169,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41502</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41507</v>
       </c>
       <c r="C18" t="n">
@@ -11189,10 +11201,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41593</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41597</v>
       </c>
       <c r="C19" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41705</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41711</v>
       </c>
       <c r="C20" t="n">
@@ -11253,10 +11265,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41775</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41780</v>
       </c>
       <c r="C21" t="n">
@@ -11285,10 +11297,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41866</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41871</v>
       </c>
       <c r="C22" t="n">
@@ -11317,10 +11329,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41957</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41962</v>
       </c>
       <c r="C23" t="n">
@@ -11349,10 +11361,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42069</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42075</v>
       </c>
       <c r="C24" t="n">
@@ -11381,10 +11393,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42139</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42144</v>
       </c>
       <c r="C25" t="n">
@@ -11413,10 +11425,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42230</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42235</v>
       </c>
       <c r="C26" t="n">
@@ -11445,10 +11457,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42321</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42326</v>
       </c>
       <c r="C27" t="n">
@@ -11477,10 +11489,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42440</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42446</v>
       </c>
       <c r="C28" t="n">
@@ -11509,10 +11521,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42513</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42515</v>
       </c>
       <c r="C29" t="n">
@@ -11541,10 +11553,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42601</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42605</v>
       </c>
       <c r="C30" t="n">
@@ -11573,10 +11585,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42692</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="C31" t="n">
@@ -11605,10 +11617,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42790</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="C32" t="n">
@@ -11637,10 +11649,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42874</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="C33" t="n">
@@ -11669,10 +11681,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42965</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42970</v>
       </c>
       <c r="C34" t="n">
@@ -11701,10 +11713,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43056</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43060</v>
       </c>
       <c r="C35" t="n">
@@ -11733,10 +11745,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43157</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="C36" t="n">
@@ -11765,10 +11777,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43238</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="C37" t="n">
@@ -11797,10 +11809,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43322</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43328</v>
       </c>
       <c r="C38" t="n">
@@ -11829,10 +11841,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43413</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43419</v>
       </c>
       <c r="C39" t="n">
@@ -11861,10 +11873,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43511</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C40" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43595</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43601</v>
       </c>
       <c r="C41" t="n">
@@ -11925,10 +11937,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43686</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43692</v>
       </c>
       <c r="C42" t="n">
@@ -11957,10 +11969,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43777</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43783</v>
       </c>
       <c r="C43" t="n">
@@ -11989,10 +12001,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43875</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="C44" t="n">
@@ -12021,10 +12033,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43966</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="C45" t="n">
@@ -12053,10 +12065,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44057</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44062</v>
       </c>
       <c r="C46" t="n">
@@ -12085,10 +12097,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44148</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44153</v>
       </c>
       <c r="C47" t="n">
@@ -12117,10 +12129,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44246</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C48" t="n">
@@ -12149,10 +12161,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44337</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44342</v>
       </c>
       <c r="C49" t="n">
@@ -12181,10 +12193,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44421</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="C50" t="n">
@@ -12213,10 +12225,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44512</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44522</v>
       </c>
       <c r="C51" t="n">
@@ -12245,10 +12257,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44631</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="C52" t="n">
@@ -12277,10 +12289,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44701</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="C53" t="n">
@@ -12309,10 +12321,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44792</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="C54" t="n">
@@ -12341,10 +12353,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44876</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="C55" t="n">
@@ -12373,10 +12385,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44974</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="C56" t="n">
@@ -12405,10 +12417,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45065</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="C57" t="n">
@@ -12437,10 +12449,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45156</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45166</v>
       </c>
       <c r="C58" t="n">
@@ -12469,10 +12481,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45247</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="C59" t="n">
@@ -12501,10 +12513,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="C60" t="n">
@@ -12533,10 +12545,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45436</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45441</v>
       </c>
       <c r="C61" t="n">
@@ -12565,10 +12577,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45527</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45532</v>
       </c>
       <c r="C62" t="n">
@@ -12597,10 +12609,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45611</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45616</v>
       </c>
       <c r="C63" t="n">
@@ -12629,10 +12641,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45709</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="C64" t="n">
@@ -12661,10 +12673,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45800</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="C65" t="n">
@@ -12693,10 +12705,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45891</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="C66" t="n">
@@ -12725,10 +12737,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45975</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45980</v>
       </c>
       <c r="C67" t="n">
@@ -12757,10 +12769,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="C68" t="n">
@@ -12789,10 +12801,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46162</v>
       </c>
       <c r="C69" t="n">
@@ -12821,10 +12833,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46255</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46260</v>
       </c>
       <c r="C70" t="n">
@@ -12871,12 +12883,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -13014,7 +13026,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2000-06-27 2:1; 2001-09-12 2:1; 2006-04-07 2:1; 2007-09-11 1.5:1; 2021-07-20 4:1; 2024-06-10 10:1</t>
+          <t>2000-06-27 2:1; 2001-09-10 2:1; 2006-04-07 2:1; 2007-09-11 1.5:1; 2021-07-20 4:1; 2024-06-10 10:1</t>
         </is>
       </c>
     </row>

--- a/salidas/empresas/NVDA.xlsx
+++ b/salidas/empresas/NVDA.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3427056968212128</v>
+        <v>0.3427056670188904</v>
       </c>
       <c r="C2" t="n">
         <v>0.3746669888496399</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3592460751533508</v>
+        <v>0.3592461049556732</v>
       </c>
       <c r="C3" t="n">
         <v>0.3927499949932098</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4364618062973022</v>
+        <v>0.4364619255065918</v>
       </c>
       <c r="C4" t="n">
         <v>0.477167010307312</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4454559683799744</v>
+        <v>0.4454559981822968</v>
       </c>
       <c r="C5" t="n">
         <v>0.4869999885559082</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3503278493881226</v>
+        <v>0.3503278195858002</v>
       </c>
       <c r="C6" t="n">
         <v>0.382999986410141</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3245636522769928</v>
+        <v>0.3245636224746704</v>
       </c>
       <c r="C7" t="n">
         <v>0.3548330068588257</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3375221788883209</v>
+        <v>0.3375221490859985</v>
       </c>
       <c r="C8" t="n">
         <v>0.3689999878406525</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437792897224426</v>
+        <v>0.443779319524765</v>
       </c>
       <c r="C9" t="n">
         <v>0.485166996717453</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4510968327522278</v>
+        <v>0.4510968625545502</v>
       </c>
       <c r="C10" t="n">
         <v>0.4931670129299164</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5315897464752197</v>
+        <v>0.5315898656845093</v>
       </c>
       <c r="C11" t="n">
         <v>0.5811669826507568</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5639087557792664</v>
+        <v>0.5639088153839111</v>
       </c>
       <c r="C12" t="n">
         <v>0.6165000200271606</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5642133951187134</v>
+        <v>0.5642134547233582</v>
       </c>
       <c r="C13" t="n">
         <v>0.616832971572876</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4672559201717377</v>
+        <v>0.4672558307647705</v>
       </c>
       <c r="C14" t="n">
         <v>0.5108330249786377</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>0.4725921750068665</v>
+        <v>0.4725920855998993</v>
       </c>
       <c r="C15" t="n">
         <v>0.5166670083999634</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5014051198959351</v>
+        <v>0.5014051795005798</v>
       </c>
       <c r="C17" t="n">
         <v>0.5481669902801514</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5280829668045044</v>
+        <v>0.5280830264091492</v>
       </c>
       <c r="C18" t="n">
         <v>0.5773329734802246</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6297668814659119</v>
+        <v>0.6297668218612671</v>
       </c>
       <c r="C19" t="n">
         <v>0.6884999871253967</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6976071000099182</v>
+        <v>0.6976070404052734</v>
       </c>
       <c r="C20" t="n">
         <v>0.7626670002937317</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7799292802810669</v>
+        <v>0.7799296379089355</v>
       </c>
       <c r="C21" t="n">
         <v>0.852666974067688</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>0.8090469837188721</v>
+        <v>0.8090470433235168</v>
       </c>
       <c r="C23" t="n">
         <v>0.8845000267028809</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>0.7212361693382263</v>
+        <v>0.7212364077568054</v>
       </c>
       <c r="C24" t="n">
         <v>0.7885000109672546</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>0.5623083114624023</v>
+        <v>0.5623082518577576</v>
       </c>
       <c r="C26" t="n">
         <v>0.6147500276565552</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>0.4525448381900787</v>
+        <v>0.4525448977947235</v>
       </c>
       <c r="C28" t="n">
         <v>0.4947499930858612</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>0.4699239432811737</v>
+        <v>0.4699240922927856</v>
       </c>
       <c r="C29" t="n">
         <v>0.5137500166893005</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>0.5648238658905029</v>
+        <v>0.5648235082626343</v>
       </c>
       <c r="C30" t="n">
         <v>0.6175000071525574</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>0.261602371931076</v>
+        <v>0.2616025507450104</v>
       </c>
       <c r="C32" t="n">
         <v>0.2860000133514404</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>0.2890433967113495</v>
+        <v>0.2890433371067047</v>
       </c>
       <c r="C33" t="n">
         <v>0.3160000145435333</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>0.244909331202507</v>
+        <v>0.2449093908071518</v>
       </c>
       <c r="C34" t="n">
         <v>0.2677499949932098</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>0.2003179937601089</v>
+        <v>0.2003179788589478</v>
       </c>
       <c r="C35" t="n">
         <v>0.2189999967813492</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1708190888166428</v>
+        <v>0.1708191484212875</v>
       </c>
       <c r="C36" t="n">
         <v>0.1867499947547913</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1817953586578369</v>
+        <v>0.1817954033613205</v>
       </c>
       <c r="C38" t="n">
         <v>0.1987500041723251</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1893417239189148</v>
+        <v>0.1893416792154312</v>
       </c>
       <c r="C39" t="n">
         <v>0.2070000022649765</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>0.2625171840190887</v>
+        <v>0.2625172436237335</v>
       </c>
       <c r="C41" t="n">
         <v>0.2870000004768372</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>0.238506481051445</v>
+        <v>0.2385064214468002</v>
       </c>
       <c r="C42" t="n">
         <v>0.2607499957084656</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>0.2581723630428314</v>
+        <v>0.2581722438335419</v>
       </c>
       <c r="C43" t="n">
         <v>0.2822499871253967</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>0.2956749200820923</v>
+        <v>0.2956749498844147</v>
       </c>
       <c r="C44" t="n">
         <v>0.3232499957084656</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3320339620113373</v>
+        <v>0.3320340216159821</v>
       </c>
       <c r="C45" t="n">
         <v>0.3630000054836273</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>0.3436962962150574</v>
+        <v>0.343696266412735</v>
       </c>
       <c r="C46" t="n">
         <v>0.3757500052452087</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>0.2734933793544769</v>
+        <v>0.2734935879707336</v>
       </c>
       <c r="C47" t="n">
         <v>0.2989999949932098</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>0.2986474931240082</v>
+        <v>0.2986476123332977</v>
       </c>
       <c r="C48" t="n">
         <v>0.3264999985694885</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>0.427162230014801</v>
+        <v>0.4271621406078339</v>
       </c>
       <c r="C49" t="n">
         <v>0.4670000076293945</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>0.3519285321235657</v>
+        <v>0.3519284725189209</v>
       </c>
       <c r="C50" t="n">
         <v>0.3847500085830688</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>0.3704510629177094</v>
+        <v>0.3704511225223541</v>
       </c>
       <c r="C51" t="n">
         <v>0.4050000011920929</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>0.3978918492794037</v>
+        <v>0.3978918790817261</v>
       </c>
       <c r="C52" t="n">
         <v>0.4350000023841858</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>0.3592460751533508</v>
+        <v>0.3592461049556732</v>
       </c>
       <c r="C53" t="n">
         <v>0.3927499949932098</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>0.3004769682884216</v>
+        <v>0.3004770278930664</v>
       </c>
       <c r="C54" t="n">
         <v>0.3285000026226044</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>0.2334756553173065</v>
+        <v>0.2334756702184677</v>
       </c>
       <c r="C55" t="n">
         <v>0.2552500069141388</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>0.2101509869098663</v>
+        <v>0.2101509571075439</v>
       </c>
       <c r="C56" t="n">
         <v>0.229750007390976</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>0.2133524268865585</v>
+        <v>0.2133523672819138</v>
       </c>
       <c r="C57" t="n">
         <v>0.2332500070333481</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>0.2670906484127045</v>
+        <v>0.2670905888080597</v>
       </c>
       <c r="C58" t="n">
         <v>0.2919999957084656</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>0.3112246692180634</v>
+        <v>0.3112245798110962</v>
       </c>
       <c r="C60" t="n">
         <v>0.3402499854564667</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>0.3521571159362793</v>
+        <v>0.3521571457386017</v>
       </c>
       <c r="C61" t="n">
         <v>0.3849999904632568</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>0.5469867587089539</v>
+        <v>0.5469871759414673</v>
       </c>
       <c r="C62" t="n">
         <v>0.5979999899864197</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>0.5181741714477539</v>
+        <v>0.5181742906570435</v>
       </c>
       <c r="C63" t="n">
         <v>0.5665000081062317</v>
@@ -1819,7 +1819,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>0.4573468863964081</v>
+        <v>0.4573470056056976</v>
       </c>
       <c r="C65" t="n">
         <v>0.5</v>
@@ -1848,7 +1848,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>0.4582617282867432</v>
+        <v>0.4582615792751312</v>
       </c>
       <c r="C66" t="n">
         <v>0.5009999871253967</v>
@@ -1877,7 +1877,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>0.3645055592060089</v>
+        <v>0.3645054697990417</v>
       </c>
       <c r="C67" t="n">
         <v>0.398499995470047</v>
@@ -1906,7 +1906,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>0.316255509853363</v>
+        <v>0.3162554800510406</v>
       </c>
       <c r="C68" t="n">
         <v>0.3457500040531158</v>
@@ -1935,7 +1935,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>0.3043645024299622</v>
+        <v>0.3043643832206726</v>
       </c>
       <c r="C69" t="n">
         <v>0.332749992609024</v>
@@ -1964,7 +1964,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>0.2860705256462097</v>
+        <v>0.286070704460144</v>
       </c>
       <c r="C70" t="n">
         <v>0.3127500116825104</v>
@@ -1993,7 +1993,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>0.3384368419647217</v>
+        <v>0.3384368121623993</v>
       </c>
       <c r="C71" t="n">
         <v>0.3700000047683716</v>
@@ -2022,7 +2022,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>0.3574167490005493</v>
+        <v>0.357416570186615</v>
       </c>
       <c r="C72" t="n">
         <v>0.390749990940094</v>
@@ -2051,7 +2051,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>0.3169415891170502</v>
+        <v>0.316941499710083</v>
       </c>
       <c r="C73" t="n">
         <v>0.3465000092983246</v>
@@ -2080,7 +2080,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>0.3377506732940674</v>
+        <v>0.3377507328987122</v>
       </c>
       <c r="C74" t="n">
         <v>0.3692499995231628</v>
@@ -2109,7 +2109,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>0.3464404046535492</v>
+        <v>0.3464403450489044</v>
       </c>
       <c r="C75" t="n">
         <v>0.3787499964237213</v>
@@ -2138,7 +2138,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>0.3521571159362793</v>
+        <v>0.3521571457386017</v>
       </c>
       <c r="C76" t="n">
         <v>0.3849999904632568</v>
@@ -2167,7 +2167,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>0.2972756028175354</v>
+        <v>0.2972755134105682</v>
       </c>
       <c r="C77" t="n">
         <v>0.324999988079071</v>
@@ -2196,7 +2196,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>0.2842411994934082</v>
+        <v>0.2842412292957306</v>
       </c>
       <c r="C78" t="n">
         <v>0.3107500076293945</v>
@@ -2225,7 +2225,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3160268068313599</v>
+        <v>0.3160267174243927</v>
       </c>
       <c r="C79" t="n">
         <v>0.3454999923706055</v>
@@ -2283,7 +2283,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>0.3208289742469788</v>
+        <v>0.3208289444446564</v>
       </c>
       <c r="C81" t="n">
         <v>0.3507499992847443</v>
@@ -2341,7 +2341,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>0.2739508450031281</v>
+        <v>0.2739509046077728</v>
       </c>
       <c r="C83" t="n">
         <v>0.2994999885559082</v>
@@ -2370,7 +2370,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>0.2754880487918854</v>
+        <v>0.2754881680011749</v>
       </c>
       <c r="C84" t="n">
         <v>0.2992500066757202</v>
@@ -2399,7 +2399,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>0.2821623682975769</v>
+        <v>0.2821624875068665</v>
       </c>
       <c r="C85" t="n">
         <v>0.3064999878406525</v>
@@ -2428,7 +2428,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>0.2821623682975769</v>
+        <v>0.2821624875068665</v>
       </c>
       <c r="C86" t="n">
         <v>0.3064999878406525</v>
@@ -2457,7 +2457,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>0.2931559085845947</v>
+        <v>0.2931559979915619</v>
       </c>
       <c r="C87" t="n">
         <v>0.3165000081062317</v>
@@ -2486,7 +2486,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>0.2970925867557526</v>
+        <v>0.2970925569534302</v>
       </c>
       <c r="C88" t="n">
         <v>0.3207499980926514</v>
@@ -2515,7 +2515,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>0.3188592195510864</v>
+        <v>0.318859338760376</v>
       </c>
       <c r="C89" t="n">
         <v>0.3442499935626984</v>
@@ -2544,7 +2544,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>0.3367703855037689</v>
+        <v>0.3367704451084137</v>
       </c>
       <c r="C90" t="n">
         <v>0.3617500066757202</v>
@@ -2573,7 +2573,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>0.3267627358436584</v>
+        <v>0.3267627060413361</v>
       </c>
       <c r="C91" t="n">
         <v>0.3510000109672546</v>
@@ -2602,7 +2602,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>0.33607217669487</v>
+        <v>0.3360720872879028</v>
       </c>
       <c r="C92" t="n">
         <v>0.3610000014305115</v>
@@ -2631,7 +2631,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>0.3450179100036621</v>
+        <v>0.3450179696083069</v>
       </c>
       <c r="C93" t="n">
         <v>0.3687500059604645</v>
@@ -2660,7 +2660,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>0.3639647960662842</v>
+        <v>0.3639646768569946</v>
       </c>
       <c r="C94" t="n">
         <v>0.3889999985694885</v>
@@ -2689,7 +2689,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>0.3553100526332855</v>
+        <v>0.3553099632263184</v>
       </c>
       <c r="C95" t="n">
         <v>0.3797500133514404</v>
@@ -2718,7 +2718,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>0.3668765723705292</v>
+        <v>0.3668765425682068</v>
       </c>
       <c r="C96" t="n">
         <v>0.3899999856948853</v>
@@ -2747,7 +2747,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>0.3767539262771606</v>
+        <v>0.3767539858818054</v>
       </c>
       <c r="C97" t="n">
         <v>0.4004999995231628</v>
@@ -2776,7 +2776,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>0.3692283034324646</v>
+        <v>0.3692283630371094</v>
       </c>
       <c r="C98" t="n">
         <v>0.3925000131130219</v>
@@ -2805,7 +2805,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>0.4342076480388641</v>
+        <v>0.4342076778411865</v>
       </c>
       <c r="C99" t="n">
         <v>0.4595000147819519</v>
@@ -2834,7 +2834,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>0.4231043457984924</v>
+        <v>0.4231044352054596</v>
       </c>
       <c r="C100" t="n">
         <v>0.4477500021457672</v>
@@ -2892,7 +2892,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>0.4509216248989105</v>
+        <v>0.4509218037128448</v>
       </c>
       <c r="C102" t="n">
         <v>0.4749999940395355</v>
@@ -2921,7 +2921,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>0.4400047361850739</v>
+        <v>0.4400047063827515</v>
       </c>
       <c r="C103" t="n">
         <v>0.4634999930858612</v>
@@ -2950,7 +2950,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>0.4153225719928741</v>
+        <v>0.4153226912021637</v>
       </c>
       <c r="C104" t="n">
         <v>0.4375</v>
@@ -2979,7 +2979,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>0.4636434316635132</v>
+        <v>0.4636436104774475</v>
       </c>
       <c r="C105" t="n">
         <v>0.4862500131130219</v>
@@ -3008,7 +3008,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>0.4398057162761688</v>
+        <v>0.4398058354854584</v>
       </c>
       <c r="C106" t="n">
         <v>0.4612500071525574</v>
@@ -3037,7 +3037,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>0.4657887816429138</v>
+        <v>0.4657887518405914</v>
       </c>
       <c r="C107" t="n">
         <v>0.4884999990463257</v>
@@ -3066,7 +3066,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>0.5019922852516174</v>
+        <v>0.5019921660423279</v>
       </c>
       <c r="C108" t="n">
         <v>0.5242499709129333</v>
@@ -3095,7 +3095,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>0.4799687266349792</v>
+        <v>0.4799687564373016</v>
       </c>
       <c r="C109" t="n">
         <v>0.5012500286102295</v>
@@ -3153,7 +3153,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>0.5301188826560974</v>
+        <v>0.5301187038421631</v>
       </c>
       <c r="C111" t="n">
         <v>0.5515000224113464</v>
@@ -3182,7 +3182,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>0.5029641389846802</v>
+        <v>0.5029639005661011</v>
       </c>
       <c r="C112" t="n">
         <v>0.5232499837875366</v>
@@ -3211,7 +3211,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>0.5334831476211548</v>
+        <v>0.5334832668304443</v>
       </c>
       <c r="C113" t="n">
         <v>0.5550000071525574</v>
@@ -3240,7 +3240,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>0.5342623591423035</v>
+        <v>0.5342625975608826</v>
       </c>
       <c r="C114" t="n">
         <v>0.5532500147819519</v>
@@ -3298,7 +3298,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>0.4816329181194305</v>
+        <v>0.4816328883171082</v>
       </c>
       <c r="C116" t="n">
         <v>0.4987500011920929</v>
@@ -3327,7 +3327,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>0.5449955463409424</v>
+        <v>0.5449956655502319</v>
       </c>
       <c r="C117" t="n">
         <v>0.5619999766349792</v>
@@ -3356,7 +3356,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>0.5976039171218872</v>
+        <v>0.5976042747497559</v>
       </c>
       <c r="C118" t="n">
         <v>0.6162499785423279</v>
@@ -3385,7 +3385,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>0.6877904534339905</v>
+        <v>0.6877902746200562</v>
       </c>
       <c r="C119" t="n">
         <v>0.7092499732971191</v>
@@ -3414,7 +3414,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>0.7719263434410095</v>
+        <v>0.7719262838363647</v>
       </c>
       <c r="C120" t="n">
         <v>0.7929999828338623</v>
@@ -3443,7 +3443,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>0.8021024465560913</v>
+        <v>0.8021025657653809</v>
       </c>
       <c r="C121" t="n">
         <v>0.8240000009536743</v>
@@ -3472,7 +3472,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>0.7127904891967773</v>
+        <v>0.7127906084060669</v>
       </c>
       <c r="C122" t="n">
         <v>0.7322499752044678</v>
@@ -3501,7 +3501,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>0.7659459114074707</v>
+        <v>0.765946090221405</v>
       </c>
       <c r="C123" t="n">
         <v>0.7839999794960022</v>
@@ -3530,7 +3530,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>0.8702377080917358</v>
+        <v>0.8702376484870911</v>
       </c>
       <c r="C124" t="n">
         <v>0.890749990940094</v>
@@ -3559,7 +3559,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>0.8677952289581299</v>
+        <v>0.8677952885627747</v>
       </c>
       <c r="C125" t="n">
         <v>0.8882499933242798</v>
@@ -3588,7 +3588,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>1.144066214561462</v>
+        <v>1.144065856933594</v>
       </c>
       <c r="C126" t="n">
         <v>1.167999982833862</v>
@@ -3617,7 +3617,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>1.151167750358582</v>
+        <v>1.151167869567871</v>
       </c>
       <c r="C127" t="n">
         <v>1.175250053405762</v>
@@ -3646,7 +3646,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>1.39824903011322</v>
+        <v>1.398248672485352</v>
       </c>
       <c r="C128" t="n">
         <v>1.427500009536743</v>
@@ -3675,7 +3675,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>1.504844427108765</v>
+        <v>1.504844665527344</v>
       </c>
       <c r="C129" t="n">
         <v>1.533499956130981</v>
@@ -3704,7 +3704,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>1.68099045753479</v>
+        <v>1.680991053581238</v>
       </c>
       <c r="C130" t="n">
         <v>1.713000059127808</v>
@@ -3733,7 +3733,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>1.745757460594177</v>
+        <v>1.745757579803467</v>
       </c>
       <c r="C131" t="n">
         <v>1.779000043869019</v>
@@ -3791,7 +3791,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>2.622555732727051</v>
+        <v>2.622556686401367</v>
       </c>
       <c r="C133" t="n">
         <v>2.668499946594238</v>
@@ -3820,7 +3820,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>2.682506322860718</v>
+        <v>2.68250584602356</v>
       </c>
       <c r="C134" t="n">
         <v>2.72950005531311</v>
@@ -3849,7 +3849,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>2.496467113494873</v>
+        <v>2.496466875076294</v>
       </c>
       <c r="C135" t="n">
         <v>2.536999940872192</v>
@@ -3878,7 +3878,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>2.679741621017456</v>
+        <v>2.679742097854614</v>
       </c>
       <c r="C136" t="n">
         <v>2.723249912261963</v>
@@ -3907,7 +3907,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>2.56584095954895</v>
+        <v>2.565840482711792</v>
       </c>
       <c r="C137" t="n">
         <v>2.607500076293945</v>
@@ -3965,7 +3965,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>3.560006141662598</v>
+        <v>3.560005664825439</v>
       </c>
       <c r="C139" t="n">
         <v>3.614000082015991</v>
@@ -3994,7 +3994,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>4.00205135345459</v>
+        <v>4.002050399780273</v>
       </c>
       <c r="C140" t="n">
         <v>4.062749862670898</v>
@@ -4023,7 +4023,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>4.17638635635376</v>
+        <v>4.176386833190918</v>
       </c>
       <c r="C141" t="n">
         <v>4.236000061035156</v>
@@ -4052,7 +4052,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>4.406354904174805</v>
+        <v>4.406354427337646</v>
       </c>
       <c r="C142" t="n">
         <v>4.469250202178955</v>
@@ -4081,7 +4081,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>5.097489833831787</v>
+        <v>5.097488403320312</v>
       </c>
       <c r="C143" t="n">
         <v>5.170249938964844</v>
@@ -4110,7 +4110,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>4.95057201385498</v>
+        <v>4.950571060180664</v>
       </c>
       <c r="C144" t="n">
         <v>5.017749786376953</v>
@@ -4139,7 +4139,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>4.772735118865967</v>
+        <v>4.772736072540283</v>
       </c>
       <c r="C145" t="n">
         <v>4.837500095367432</v>
@@ -4197,7 +4197,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>5.972710609436035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="C147" t="n">
         <v>6.050000190734863</v>
@@ -4255,7 +4255,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>5.550673961639404</v>
+        <v>5.550673484802246</v>
       </c>
       <c r="C149" t="n">
         <v>5.622499942779541</v>
@@ -4284,7 +4284,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>6.228057861328125</v>
+        <v>6.228056907653809</v>
       </c>
       <c r="C150" t="n">
         <v>6.304749965667725</v>
@@ -4313,7 +4313,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>5.850456237792969</v>
+        <v>5.850457191467285</v>
       </c>
       <c r="C151" t="n">
         <v>5.922500133514404</v>
@@ -4342,7 +4342,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>6.047036170959473</v>
+        <v>6.047035694122314</v>
       </c>
       <c r="C152" t="n">
         <v>6.121500015258789</v>
@@ -4371,7 +4371,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>6.935435771942139</v>
+        <v>6.935433864593506</v>
       </c>
       <c r="C153" t="n">
         <v>7.017000198364258</v>
@@ -4400,7 +4400,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>6.94383430480957</v>
+        <v>6.943834781646729</v>
       </c>
       <c r="C154" t="n">
         <v>7.025499820709229</v>
@@ -4429,7 +4429,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>5.209482192993164</v>
+        <v>5.209482669830322</v>
       </c>
       <c r="C155" t="n">
         <v>5.270750045776367</v>
@@ -4458,7 +4458,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>4.042296886444092</v>
+        <v>4.042299747467041</v>
       </c>
       <c r="C156" t="n">
         <v>4.085750102996826</v>
@@ -4487,7 +4487,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>3.302005529403687</v>
+        <v>3.302005290985107</v>
       </c>
       <c r="C157" t="n">
         <v>3.337500095367432</v>
@@ -4516,7 +4516,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>3.555529594421387</v>
+        <v>3.555529832839966</v>
       </c>
       <c r="C158" t="n">
         <v>3.59375</v>
@@ -4574,7 +4574,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>4.445836544036865</v>
+        <v>4.445836067199707</v>
       </c>
       <c r="C160" t="n">
         <v>4.488999843597412</v>
@@ -4603,7 +4603,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>4.481490612030029</v>
+        <v>4.481491088867188</v>
       </c>
       <c r="C161" t="n">
         <v>4.525000095367432</v>
@@ -4632,7 +4632,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>3.357765674591064</v>
+        <v>3.357765197753906</v>
       </c>
       <c r="C162" t="n">
         <v>3.386499881744385</v>
@@ -4719,7 +4719,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>4.156328201293945</v>
+        <v>4.156326770782471</v>
       </c>
       <c r="C165" t="n">
         <v>4.187749862670898</v>
@@ -4748,7 +4748,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>4.31909704208374</v>
+        <v>4.319096565246582</v>
       </c>
       <c r="C166" t="n">
         <v>4.351749897003174</v>
@@ -4806,7 +4806,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>5.381809711456299</v>
+        <v>5.381810188293457</v>
       </c>
       <c r="C168" t="n">
         <v>5.418499946594238</v>
@@ -4864,7 +4864,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>5.870725154876709</v>
+        <v>5.870725631713867</v>
       </c>
       <c r="C170" t="n">
         <v>5.910749912261963</v>
@@ -4922,7 +4922,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>6.549293041229248</v>
+        <v>6.54929256439209</v>
       </c>
       <c r="C172" t="n">
         <v>6.590000152587891</v>
@@ -4951,7 +4951,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>7.261863708496094</v>
+        <v>7.261864185333252</v>
       </c>
       <c r="C173" t="n">
         <v>7.307000160217285</v>
@@ -4980,7 +4980,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>8.820673942565918</v>
+        <v>8.820675849914551</v>
       </c>
       <c r="C174" t="n">
         <v>8.875499725341797</v>
@@ -5009,7 +5009,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>9.443389892578125</v>
+        <v>9.443388938903809</v>
       </c>
       <c r="C175" t="n">
         <v>9.497750282287598</v>
@@ -5038,7 +5038,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>10.55399417877197</v>
+        <v>10.55399703979492</v>
       </c>
       <c r="C176" t="n">
         <v>10.61474990844727</v>
@@ -5067,7 +5067,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>13.29795074462891</v>
+        <v>13.29794883728027</v>
       </c>
       <c r="C177" t="n">
         <v>13.3745002746582</v>
@@ -5125,7 +5125,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>12.46598720550537</v>
+        <v>12.465989112854</v>
       </c>
       <c r="C179" t="n">
         <v>12.53400039672852</v>
@@ -5154,7 +5154,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>13.32878112792969</v>
+        <v>13.328782081604</v>
       </c>
       <c r="C180" t="n">
         <v>13.40149974822998</v>
@@ -5183,7 +5183,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>12.98799991607666</v>
+        <v>12.98799800872803</v>
       </c>
       <c r="C181" t="n">
         <v>13.05500030517578</v>
@@ -5212,7 +5212,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>12.92308044433594</v>
+        <v>12.92308521270752</v>
       </c>
       <c r="C182" t="n">
         <v>12.98974990844727</v>
@@ -5270,7 +5270,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>13.28432464599609</v>
+        <v>13.28432655334473</v>
       </c>
       <c r="C184" t="n">
         <v>13.34825038909912</v>
@@ -5299,7 +5299,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>14.93761920928955</v>
+        <v>14.9376220703125</v>
       </c>
       <c r="C185" t="n">
         <v>15.00949954986572</v>
@@ -5357,7 +5357,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>19.91127395629883</v>
+        <v>19.91127586364746</v>
       </c>
       <c r="C187" t="n">
         <v>20.00250053405762</v>
@@ -5386,7 +5386,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>19.41006851196289</v>
+        <v>19.41007041931152</v>
       </c>
       <c r="C188" t="n">
         <v>19.49900054931641</v>
@@ -5415,7 +5415,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>22.28683853149414</v>
+        <v>22.28683471679688</v>
       </c>
       <c r="C189" t="n">
         <v>22.38500022888184</v>
@@ -5473,7 +5473,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>25.45487785339355</v>
+        <v>25.45488357543945</v>
       </c>
       <c r="C191" t="n">
         <v>25.5669994354248</v>
@@ -5502,7 +5502,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>32.5327033996582</v>
+        <v>32.53269958496094</v>
       </c>
       <c r="C192" t="n">
         <v>32.67599868774414</v>
@@ -5531,7 +5531,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>29.28561019897461</v>
+        <v>29.28560829162598</v>
       </c>
       <c r="C193" t="n">
         <v>29.4109992980957</v>
@@ -5560,7 +5560,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>24.3816032409668</v>
+        <v>24.38161087036133</v>
       </c>
       <c r="C194" t="n">
         <v>24.48600006103516</v>
@@ -5618,7 +5618,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>27.1742992401123</v>
+        <v>27.17430114746094</v>
       </c>
       <c r="C196" t="n">
         <v>27.2859992980957</v>
@@ -5647,7 +5647,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>18.47107315063477</v>
+        <v>18.47107696533203</v>
       </c>
       <c r="C197" t="n">
         <v>18.54700088500977</v>
@@ -5792,7 +5792,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>12.09545421600342</v>
+        <v>12.0954532623291</v>
       </c>
       <c r="C202" t="n">
         <v>12.13899993896484</v>
@@ -5821,7 +5821,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>13.44858169555664</v>
+        <v>13.44858360290527</v>
       </c>
       <c r="C203" t="n">
         <v>13.49699974060059</v>
@@ -5850,7 +5850,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>16.86660385131836</v>
+        <v>16.86660766601562</v>
       </c>
       <c r="C204" t="n">
         <v>16.92300033569336</v>
@@ -5879,7 +5879,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>14.5653018951416</v>
+        <v>14.56529998779297</v>
       </c>
       <c r="C205" t="n">
         <v>14.61400032043457</v>
@@ -5908,7 +5908,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>19.47190093994141</v>
+        <v>19.47189712524414</v>
       </c>
       <c r="C206" t="n">
         <v>19.53700065612793</v>
@@ -5966,7 +5966,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>27.68914413452148</v>
+        <v>27.68914031982422</v>
       </c>
       <c r="C208" t="n">
         <v>27.77700042724609</v>
@@ -6024,7 +6024,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>37.71432876586914</v>
+        <v>37.71433258056641</v>
       </c>
       <c r="C210" t="n">
         <v>37.83399963378906</v>
@@ -6053,7 +6053,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>42.17256164550781</v>
+        <v>42.17256546020508</v>
       </c>
       <c r="C211" t="n">
         <v>42.30199813842773</v>
@@ -6082,7 +6082,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>46.58601379394531</v>
+        <v>46.58600997924805</v>
       </c>
       <c r="C212" t="n">
         <v>46.72900009155273</v>
@@ -6111,7 +6111,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>49.20398330688477</v>
+        <v>49.2039794921875</v>
       </c>
       <c r="C213" t="n">
         <v>49.35499954223633</v>
@@ -6169,7 +6169,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>40.6585693359375</v>
+        <v>40.65856552124023</v>
       </c>
       <c r="C215" t="n">
         <v>40.77999877929688</v>
@@ -6198,7 +6198,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>46.6307373046875</v>
+        <v>46.63072967529297</v>
       </c>
       <c r="C216" t="n">
         <v>46.77000045776367</v>
@@ -6256,7 +6256,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>61.34918594360352</v>
+        <v>61.34918975830078</v>
       </c>
       <c r="C218" t="n">
         <v>61.52700042724609</v>
@@ -6314,7 +6314,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>90.09909820556641</v>
+        <v>90.09909057617188</v>
       </c>
       <c r="C220" t="n">
         <v>90.35600280761719</v>
@@ -6343,7 +6343,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>86.15634155273438</v>
+        <v>86.15633392333984</v>
       </c>
       <c r="C221" t="n">
         <v>86.40200042724609</v>
@@ -6372,7 +6372,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>109.3212966918945</v>
+        <v>109.3212890625</v>
       </c>
       <c r="C222" t="n">
         <v>109.6330032348633</v>
@@ -6401,7 +6401,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>123.1988525390625</v>
+        <v>123.198860168457</v>
       </c>
       <c r="C223" t="n">
         <v>123.5400009155273</v>
@@ -6459,7 +6459,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>119.0403747558594</v>
+        <v>119.0403823852539</v>
       </c>
       <c r="C225" t="n">
         <v>119.370002746582</v>
@@ -6517,7 +6517,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>132.4047241210938</v>
+        <v>132.4047088623047</v>
       </c>
       <c r="C227" t="n">
         <v>132.7599945068359</v>
@@ -6546,7 +6546,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>137.8800354003906</v>
+        <v>137.8800506591797</v>
       </c>
       <c r="C228" t="n">
         <v>138.25</v>
@@ -6575,7 +6575,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>133.9398498535156</v>
+        <v>133.9398651123047</v>
       </c>
       <c r="C229" t="n">
         <v>134.2899932861328</v>
@@ -6633,7 +6633,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>124.5942840576172</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="C231" t="n">
         <v>124.9199981689453</v>
@@ -6662,7 +6662,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>108.1073532104492</v>
+        <v>108.1073608398438</v>
       </c>
       <c r="C232" t="n">
         <v>108.379997253418</v>
@@ -6720,7 +6720,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>134.7900695800781</v>
+        <v>134.7900848388672</v>
       </c>
       <c r="C234" t="n">
         <v>135.1300048828125</v>
@@ -6749,7 +6749,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>157.6035308837891</v>
+        <v>157.603515625</v>
       </c>
       <c r="C235" t="n">
         <v>157.9900054931641</v>
@@ -6894,7 +6894,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="C240" t="n">
         <v>177</v>
@@ -7010,7 +7010,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="C244" t="n">
         <v>174.3999938964844</v>
@@ -7039,7 +7039,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="C245" t="n">
         <v>199.5700073242188</v>
